--- a/nr-prepare-ballot-release/ig/PN13-FHIR-FreeSetCIODC-Unite-ConceptMap.xlsx
+++ b/nr-prepare-ballot-release/ig/PN13-FHIR-FreeSetCIODC-Unite-ConceptMap.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-ballot</t>
+    <t>1.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
